--- a/data/trans_orig/P04B3_1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_1_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe la temperatura en la vivienda durante el verano como un problema en 2023</t>
+          <t>Población según si percibe la temperatura en la vivienda durante el verano como un problema en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>131787</t>
+          <t>130234</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168312</t>
+          <t>168050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>216076</t>
+          <t>214909</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>256708</t>
+          <t>257253</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>357038</t>
+          <t>358165</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>413458</t>
+          <t>415624</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73518</t>
+          <t>72457</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102719</t>
+          <t>101556</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105663</t>
+          <t>105788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136661</t>
+          <t>135926</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>187577</t>
+          <t>186752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>231136</t>
+          <t>228260</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50585</t>
+          <t>51361</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77633</t>
+          <t>77461</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>107261</t>
+          <t>108511</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>138568</t>
+          <t>138981</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>165156</t>
+          <t>163819</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>206269</t>
+          <t>205633</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>196532</t>
+          <t>197000</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>237489</t>
+          <t>238369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>258523</t>
+          <t>255724</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>297514</t>
+          <t>296779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>464237</t>
+          <t>462440</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>523561</t>
+          <t>521893</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>335639</t>
+          <t>341308</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>569482</t>
+          <t>573167</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>390079</t>
+          <t>396555</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>686901</t>
+          <t>682067</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>847496</t>
+          <t>836491</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1200168</t>
+          <t>1199521</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169828</t>
+          <t>170743</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>296316</t>
+          <t>298891</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>184620</t>
+          <t>183875</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>295393</t>
+          <t>292725</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>405329</t>
+          <t>398469</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>567925</t>
+          <t>564090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276439</t>
+          <t>263355</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>457024</t>
+          <t>456878</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227099</t>
+          <t>226059</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>361771</t>
+          <t>362473</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>553163</t>
+          <t>560815</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>786868</t>
+          <t>791374</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1006855</t>
+          <t>999633</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1508692</t>
+          <t>1532461</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1012283</t>
+          <t>1006500</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1462176</t>
+          <t>1448562</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2062936</t>
+          <t>2070904</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2762379</t>
+          <t>2758855</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,94%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105383</t>
+          <t>105056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146016</t>
+          <t>148215</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89325</t>
+          <t>91856</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122241</t>
+          <t>124930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208571</t>
+          <t>207707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>260313</t>
+          <t>258978</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62651</t>
+          <t>64875</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96194</t>
+          <t>99614</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70133</t>
+          <t>69609</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>97958</t>
+          <t>98970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>140384</t>
+          <t>140418</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>185510</t>
+          <t>185840</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89350</t>
+          <t>86616</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129159</t>
+          <t>127767</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>93924</t>
+          <t>95314</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128354</t>
+          <t>128271</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192735</t>
+          <t>190682</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>243434</t>
+          <t>244040</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>307317</t>
+          <t>305522</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>362888</t>
+          <t>360428</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>338883</t>
+          <t>336746</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>383188</t>
+          <t>383235</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>659656</t>
+          <t>657148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>730307</t>
+          <t>728356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,85%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>611792</t>
+          <t>592645</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>852488</t>
+          <t>844295</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>733813</t>
+          <t>729266</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1008001</t>
+          <t>1021620</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1451225</t>
+          <t>1434579</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1828677</t>
+          <t>1804529</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>319471</t>
+          <t>322735</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>470882</t>
+          <t>467770</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>383621</t>
+          <t>369197</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>509306</t>
+          <t>501308</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>754265</t>
+          <t>736307</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>946148</t>
+          <t>943236</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>430677</t>
+          <t>438192</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>625807</t>
+          <t>628378</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>439883</t>
+          <t>445664</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>598689</t>
+          <t>596521</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>960678</t>
+          <t>954119</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1197307</t>
+          <t>1201101</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1547396</t>
+          <t>1552933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2069354</t>
+          <t>2133710</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1642873</t>
+          <t>1646745</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2120081</t>
+          <t>2111938</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3252052</t>
+          <t>3245280</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3941732</t>
+          <t>4056627</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>57,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_1_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>148867</t>
+          <t>166618</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130234</t>
+          <t>146806</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168050</t>
+          <t>187860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>235756</t>
+          <t>263023</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>214909</t>
+          <t>243410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>257253</t>
+          <t>284075</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>384623</t>
+          <t>429641</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>358165</t>
+          <t>400967</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>415624</t>
+          <t>463570</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87064</t>
+          <t>100427</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72457</t>
+          <t>84093</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101556</t>
+          <t>118940</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>120776</t>
+          <t>132075</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105788</t>
+          <t>116562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135926</t>
+          <t>147686</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>207840</t>
+          <t>232502</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>186752</t>
+          <t>209225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>228260</t>
+          <t>254969</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62974</t>
+          <t>74524</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51361</t>
+          <t>60088</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77461</t>
+          <t>90539</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>122005</t>
+          <t>131845</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>108511</t>
+          <t>116304</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>138981</t>
+          <t>150486</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>184979</t>
+          <t>206369</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>163819</t>
+          <t>185646</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>205633</t>
+          <t>230674</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>216033</t>
+          <t>236960</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>197000</t>
+          <t>214207</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>238369</t>
+          <t>261027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>276971</t>
+          <t>295096</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>255724</t>
+          <t>275024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>296779</t>
+          <t>317126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>493004</t>
+          <t>532056</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>462440</t>
+          <t>496532</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>521893</t>
+          <t>566943</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,48%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>496049</t>
+          <t>578226</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>341308</t>
+          <t>536556</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>573167</t>
+          <t>627631</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>521991</t>
+          <t>529725</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>396555</t>
+          <t>491588</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>682067</t>
+          <t>570364</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1018040</t>
+          <t>1107951</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>836491</t>
+          <t>1048041</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1199521</t>
+          <t>1173880</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>249772</t>
+          <t>276725</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170743</t>
+          <t>240239</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>298891</t>
+          <t>312890</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>250849</t>
+          <t>291252</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>183875</t>
+          <t>263802</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>292725</t>
+          <t>322278</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>500621</t>
+          <t>567977</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>398469</t>
+          <t>526581</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>564090</t>
+          <t>615617</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>389753</t>
+          <t>406186</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>263355</t>
+          <t>365503</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>456878</t>
+          <t>451821</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>311532</t>
+          <t>356582</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226059</t>
+          <t>325980</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>362473</t>
+          <t>390830</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>701285</t>
+          <t>762767</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>560815</t>
+          <t>706506</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>791374</t>
+          <t>816767</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1154753</t>
+          <t>969430</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>999633</t>
+          <t>914550</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1532461</t>
+          <t>1022368</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1152831</t>
+          <t>993126</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1006500</t>
+          <t>947363</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1448562</t>
+          <t>1035985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2307585</t>
+          <t>1962556</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2070904</t>
+          <t>1899204</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2758855</t>
+          <t>2033005</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2237203</t>
+          <t>2170684</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2237203</t>
+          <t>2170684</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2237203</t>
+          <t>2170684</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4527530</t>
+          <t>4401251</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4527530</t>
+          <t>4401251</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4527530</t>
+          <t>4401251</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>126075</t>
+          <t>144934</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105056</t>
+          <t>122610</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148215</t>
+          <t>168966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>106265</t>
+          <t>118424</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>91856</t>
+          <t>100191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124930</t>
+          <t>137574</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>232340</t>
+          <t>263358</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>207707</t>
+          <t>234123</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>258978</t>
+          <t>292203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78767</t>
+          <t>88660</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64875</t>
+          <t>71890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>99614</t>
+          <t>108210</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>83145</t>
+          <t>103217</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69609</t>
+          <t>86922</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>98970</t>
+          <t>120206</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>161912</t>
+          <t>191878</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>140418</t>
+          <t>168120</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>185840</t>
+          <t>217515</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>106406</t>
+          <t>121776</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86616</t>
+          <t>100862</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127767</t>
+          <t>143582</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>109747</t>
+          <t>125615</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95314</t>
+          <t>108899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128271</t>
+          <t>146677</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>216153</t>
+          <t>247391</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>190682</t>
+          <t>217678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>244040</t>
+          <t>278262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>334194</t>
+          <t>353594</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>305522</t>
+          <t>326702</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>360428</t>
+          <t>384912</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>359599</t>
+          <t>384224</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>336746</t>
+          <t>360129</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>383235</t>
+          <t>409314</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>693794</t>
+          <t>737819</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>657148</t>
+          <t>700723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>728356</t>
+          <t>775216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>645442</t>
+          <t>708965</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>645442</t>
+          <t>708965</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>645442</t>
+          <t>708965</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>658756</t>
+          <t>731480</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>658756</t>
+          <t>731480</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>658756</t>
+          <t>731480</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1304199</t>
+          <t>1440445</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1304199</t>
+          <t>1440445</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1304199</t>
+          <t>1440445</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,67 +2432,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>770992</t>
+          <t>889778</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>592645</t>
+          <t>835282</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>844295</t>
+          <t>946089</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>26,89%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>911172</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>864017</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>960340</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
           <t>24,47%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1239</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>864012</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>729266</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1021620</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>23,66%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1635003</t>
+          <t>1800950</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1434579</t>
+          <t>1734389</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1804529</t>
+          <t>1879536</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>415603</t>
+          <t>465813</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322735</t>
+          <t>423055</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>467770</t>
+          <t>518016</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>454770</t>
+          <t>526544</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>369197</t>
+          <t>491510</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>501308</t>
+          <t>565371</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>870372</t>
+          <t>992357</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>736307</t>
+          <t>936147</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>943236</t>
+          <t>1054032</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>559133</t>
+          <t>602486</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>438192</t>
+          <t>547931</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>628378</t>
+          <t>655741</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>543285</t>
+          <t>614041</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>445664</t>
+          <t>576239</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>596521</t>
+          <t>659080</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1102417</t>
+          <t>1216527</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>954119</t>
+          <t>1148610</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1201101</t>
+          <t>1282917</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1704981</t>
+          <t>1559984</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1552933</t>
+          <t>1493198</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2133710</t>
+          <t>1628714</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1789402</t>
+          <t>1672446</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1646745</t>
+          <t>1617984</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2111938</t>
+          <t>1723896</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3494383</t>
+          <t>3232430</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3245280</t>
+          <t>3143191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4056627</t>
+          <t>3323062</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3450708</t>
+          <t>3518061</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3450708</t>
+          <t>3518061</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3450708</t>
+          <t>3518061</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3651468</t>
+          <t>3724202</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3651468</t>
+          <t>3724202</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3651468</t>
+          <t>3724202</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7102175</t>
+          <t>7242263</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7102175</t>
+          <t>7242263</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7102175</t>
+          <t>7242263</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
